--- a/it_forms/009_software_testing_device_order_request_form--it_forms.xlsx
+++ b/it_forms/009_software_testing_device_order_request_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'agreed',_'value':_'agreed'}</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Agreed', 'value': 'agreed'}</t>
+          <t>Agreed</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_agreed',_'value':_'not_agreed'}</t>
+          <t>not_agreed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not agreed', 'value': 'not_agreed'}</t>
+          <t>Not agreed</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard_shipping',_'value':_'standard_shipping'}</t>
+          <t>standard_shipping</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard Shipping', 'value': 'standard_shipping'}</t>
+          <t>Standard Shipping</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'express_shipping',_'value':_'express_shipping'}</t>
+          <t>express_shipping</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Express Shipping', 'value': 'express_shipping'}</t>
+          <t>Express Shipping</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_transit',_'value':_'in_transit'}</t>
+          <t>in_transit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In transit', 'value': 'in_transit'}</t>
+          <t>In transit</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'delivered',_'value':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Delivered', 'value': 'delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'declined',_'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Declined', 'value': 'declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
